--- a/data-vh/Неделя_16.02-22.02_2026_ВХ.xlsx
+++ b/data-vh/Неделя_16.02-22.02_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$11</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,700 +562,779 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="22.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000032</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="10" t="n">
         <v>4792.69</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, наплывы</t>
         </is>
       </c>
+      <c r="Q2" s="7" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="22.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000032</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>МК ВОЛГАДОН ООО (ЭДО Таксом ЗП согл 21.05.2024)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Стойка СП9 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="9" t="n">
         <v>656.26</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Брызги металла, наплывы</t>
         </is>
       </c>
+      <c r="Q3" s="7" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="10.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000033</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="9" t="n">
         <v>809.21</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Брызги металла</t>
         </is>
       </c>
+      <c r="Q4" s="7" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="22.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000033</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>17.02.2026</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="10" t="n">
         <v>6796.13</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, наплывы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
+      <c r="Q5" s="7" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="46.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000034</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>19.02.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ВПК-КОНЦЕПТ ООО (6312129392) (ЭДО Такском ЗП с 01.04.25)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(80 мкм / 80 мкм (RAL 9003)) Кронштейн 36.К1-2,0/1,5-2,0-Чайка-цп</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="12" t="n">
         <v>1564</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Покрытие глянцевое, VII класс. Шагрень, включения (обусловлены поверхностью цинкового покрытия), булавочные проколы, включения (не обусловленные поверхностью цинкового покрытия). Толщина ЛКП от 112 мкм до 361 мкм. Отсутствие ЛКП на отдельных участках до 1 мм (технологические отверстия).</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="22.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР18 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="10" t="n">
         <v>2342.76</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
+      <c r="Q7" s="7" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="22.95" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР17 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="10" t="n">
         <v>5560.47</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
+      <c r="Q8" s="7" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="22.95" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР7 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="10" t="n">
         <v>1174.46</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
+      <c r="Q9" s="7" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" ht="22.95" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>В00-0000035</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Секция СР6 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>РО</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="10" t="n">
         <v>1618.42</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов: брызги металла, поры, подрезы, отс. замыкание таврового шва («закольцовки»), плохое повторное возобнавление дуги.</t>
         </is>
       </c>
+      <c r="Q10" s="7" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" ht="34.95" customHeight="1">
+      <c r="A11" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>В00-0000036</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>ВПК-КОНЦЕПТ ООО (6312129392) (ЭДО Такском ЗП с 01.04.25)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(80 мкм / 80 мкм (RAL 9003)) Кронштейн 36.К1-2,0/1,5-2,0-Чайка-цп</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Покрытие глянцевое, VII класс. Шагрень, включения (обусловлены поверхностью цинкового покрытия), булавочные проколы, включения (не обусловленные поверхностью цинкового покрытия). Толщина ЛКП от 124 мкм до 493 мкм.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q11">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="11">
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>